--- a/deliverables/anforderungen/20251208_Autostrom_LKWLaden_Anforderungscockpit.xlsx
+++ b/deliverables/anforderungen/20251208_Autostrom_LKWLaden_Anforderungscockpit.xlsx
@@ -15,7 +15,6 @@
     <sheet name="Lesehilfe" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Anforderungen'!$A$6:$O$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Anforderungen'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Auswertung'!$A$1:$D$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Komponenten'!$A$5:$F$22</definedName>
@@ -4281,7 +4280,6 @@
       <c r="O58" s="17" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:O58"/>
   <conditionalFormatting sqref="J7:J58">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"ja"</formula>
